--- a/data/trans_camb/IP19C01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Edad-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 40,57</t>
+          <t>-61,96; 39,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-51,44; 40,2</t>
+          <t>-46,92; 41,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,81; 0,0</t>
+          <t>-64,2; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-65,96; 22,02</t>
+          <t>-67,51; 19,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,31</t>
+          <t>0,0; 57,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-38,68; 26,07</t>
+          <t>-38,72; 25,26</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 70,52</t>
+          <t>-79,93; 62,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,89; 76,98</t>
+          <t>-49,89; 87,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,81; 0,0</t>
+          <t>-64,2; 0,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,29; 31,52</t>
+          <t>-79,57; 18,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 105,38</t>
+          <t>0,0; 134,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 32,21</t>
+          <t>-42,31; 36,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 4,33</t>
+          <t>-15,38; 5,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 6,32</t>
+          <t>-13,98; 6,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 9,31</t>
+          <t>-10,66; 8,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 5,78</t>
+          <t>-12,51; 6,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 4,91</t>
+          <t>-14,28; 4,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 9,15</t>
+          <t>-10,58; 8,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 2,87</t>
+          <t>-11,13; 3,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 3,4</t>
+          <t>-11,73; 2,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 6,96</t>
+          <t>-7,34; 7,0</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 5,6</t>
+          <t>-17,71; 7,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 7,65</t>
+          <t>-16,16; 8,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 11,96</t>
+          <t>-12,32; 11,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 7,18</t>
+          <t>-14,49; 8,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 5,99</t>
+          <t>-16,25; 6,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 11,47</t>
+          <t>-11,99; 10,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 3,62</t>
+          <t>-12,83; 4,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 4,2</t>
+          <t>-13,46; 3,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 8,55</t>
+          <t>-8,54; 8,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 14,8</t>
+          <t>-5,4; 13,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 13,66</t>
+          <t>-6,16; 13,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 21,27</t>
+          <t>0,93; 21,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 1,62</t>
+          <t>-16,92; 1,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 6,88</t>
+          <t>-9,57; 7,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 10,15</t>
+          <t>-6,43; 10,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 5,72</t>
+          <t>-8,03; 5,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 8,18</t>
+          <t>-5,08; 7,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 13,43</t>
+          <t>-0,14; 13,08</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 23,88</t>
+          <t>-6,87; 20,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 21,5</t>
+          <t>-7,94; 20,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 33,72</t>
+          <t>1,61; 33,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 2,25</t>
+          <t>-20,1; 1,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 9,35</t>
+          <t>-11,23; 10,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 13,5</t>
+          <t>-7,71; 13,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 8,2</t>
+          <t>-10,27; 7,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 11,67</t>
+          <t>-6,36; 10,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 19,06</t>
+          <t>-0,06; 18,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,39; 22,21</t>
+          <t>3,31; 20,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 24,07</t>
+          <t>6,8; 24,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,99; 35,06</t>
+          <t>19,0; 35,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,32; 23,95</t>
+          <t>7,1; 23,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 18,5</t>
+          <t>1,49; 18,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,7; 30,36</t>
+          <t>14,51; 30,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,53; 19,81</t>
+          <t>7,6; 19,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,14; 18,76</t>
+          <t>6,65; 19,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,05; 30,61</t>
+          <t>18,94; 30,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,44; 45,13</t>
+          <t>5,9; 41,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,2; 48,9</t>
+          <t>11,67; 50,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,94; 72,42</t>
+          <t>32,01; 73,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,29; 43,58</t>
+          <t>11,65; 43,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,01; 33,33</t>
+          <t>2,76; 34,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,55; 55,51</t>
+          <t>22,66; 56,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,26; 37,13</t>
+          <t>12,76; 36,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,24; 34,74</t>
+          <t>11,4; 36,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,36; 56,68</t>
+          <t>31,71; 58,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 11,17</t>
+          <t>0,94; 11,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,01; 13,36</t>
+          <t>1,86; 13,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,99; 20,71</t>
+          <t>10,16; 20,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,78</t>
+          <t>-0,4; 9,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,83</t>
+          <t>-0,88; 9,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,87; 16,33</t>
+          <t>5,54; 16,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 9,07</t>
+          <t>1,05; 8,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,7</t>
+          <t>2,0; 9,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,37; 16,91</t>
+          <t>9,47; 17,08</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,7</t>
+          <t>1,38; 17,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,95; 21,28</t>
+          <t>2,62; 21,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14,47; 32,73</t>
+          <t>14,49; 32,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 14,23</t>
+          <t>-0,52; 14,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 14,53</t>
+          <t>-1,19; 13,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,84; 23,68</t>
+          <t>7,55; 23,58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,91; 13,51</t>
+          <t>1,47; 13,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,59</t>
+          <t>2,83; 14,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,38; 25,29</t>
+          <t>13,51; 25,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Edad-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-61,96; 39,57</t>
+          <t>-59,41; 41,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-46,92; 41,38</t>
+          <t>-48,62; 39,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-64,2; 0,0</t>
+          <t>-63,53; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,51; 19,78</t>
+          <t>-65,85; 23,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,21</t>
+          <t>0,0; 63,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 25,26</t>
+          <t>-41,81; 29,61</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,93; 62,75</t>
+          <t>-79,12; 68,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,89; 87,1</t>
+          <t>-50,98; 80,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,2; 0,0</t>
+          <t>-63,53; 0,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,57; 18,57</t>
+          <t>-77,43; 34,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 134,35</t>
+          <t>0,0; 170,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 36,83</t>
+          <t>-44,51; 42,23</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 5,51</t>
+          <t>-15,29; 5,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 6,42</t>
+          <t>-14,49; 5,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 8,75</t>
+          <t>-9,69; 10,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 6,83</t>
+          <t>-12,59; 5,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 4,96</t>
+          <t>-14,81; 4,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 8,84</t>
+          <t>-11,34; 8,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 3,23</t>
+          <t>-11,21; 3,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 2,9</t>
+          <t>-12,41; 2,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 7,0</t>
+          <t>-8,01; 6,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 7,14</t>
+          <t>-17,44; 6,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 8,22</t>
+          <t>-16,67; 7,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 11,0</t>
+          <t>-10,89; 12,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 8,36</t>
+          <t>-14,29; 6,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 6,2</t>
+          <t>-16,76; 5,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 10,81</t>
+          <t>-12,62; 11,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 4,01</t>
+          <t>-12,81; 4,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 3,62</t>
+          <t>-14,28; 3,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 8,69</t>
+          <t>-9,16; 8,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 13,55</t>
+          <t>-5,82; 13,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 13,41</t>
+          <t>-5,48; 13,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 21,29</t>
+          <t>0,62; 21,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 1,4</t>
+          <t>-16,96; 1,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 7,36</t>
+          <t>-9,62; 7,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 10,29</t>
+          <t>-6,48; 10,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 5,15</t>
+          <t>-8,25; 5,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 7,68</t>
+          <t>-5,02; 7,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 13,08</t>
+          <t>-0,19; 12,36</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 20,99</t>
+          <t>-7,64; 21,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 20,82</t>
+          <t>-7,43; 21,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 33,8</t>
+          <t>1,35; 33,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 1,83</t>
+          <t>-20,14; 1,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 10,01</t>
+          <t>-11,36; 10,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 13,63</t>
+          <t>-7,65; 14,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 7,28</t>
+          <t>-10,49; 6,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 10,73</t>
+          <t>-6,37; 10,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 18,21</t>
+          <t>-0,22; 17,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 20,68</t>
+          <t>4,12; 21,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,8; 24,74</t>
+          <t>6,99; 23,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,0; 35,54</t>
+          <t>18,0; 34,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 23,73</t>
+          <t>7,77; 23,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 18,75</t>
+          <t>1,56; 19,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,51; 30,66</t>
+          <t>13,61; 30,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,6; 19,59</t>
+          <t>7,5; 19,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 19,12</t>
+          <t>6,62; 19,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,94; 30,62</t>
+          <t>18,95; 30,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 41,78</t>
+          <t>7,2; 43,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,67; 50,58</t>
+          <t>11,63; 48,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,01; 73,72</t>
+          <t>30,19; 70,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,65; 43,62</t>
+          <t>12,78; 44,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 34,12</t>
+          <t>2,26; 36,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,66; 56,73</t>
+          <t>21,84; 55,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,76; 36,48</t>
+          <t>12,7; 36,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,4; 36,07</t>
+          <t>11,01; 35,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,71; 58,7</t>
+          <t>31,63; 58,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 11,22</t>
+          <t>0,74; 11,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 13,3</t>
+          <t>1,68; 13,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,16; 20,82</t>
+          <t>9,77; 20,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 9,88</t>
+          <t>-0,91; 9,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 9,63</t>
+          <t>-1,17; 9,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,54; 16,09</t>
+          <t>5,61; 16,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,78</t>
+          <t>1,54; 9,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,95</t>
+          <t>2,4; 10,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,47; 17,08</t>
+          <t>9,6; 17,11</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,38; 17,72</t>
+          <t>1,16; 18,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,62; 21,13</t>
+          <t>2,48; 20,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14,49; 32,87</t>
+          <t>14,21; 33,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 14,62</t>
+          <t>-1,24; 14,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 13,99</t>
+          <t>-1,58; 14,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,55; 23,58</t>
+          <t>7,54; 23,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,1</t>
+          <t>2,15; 14,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,96</t>
+          <t>3,39; 15,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,51; 25,81</t>
+          <t>13,78; 25,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-22,79</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-18,19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>19,67</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-8,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-24,98</t>
+          <t>-4,28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-13,33</t>
+          <t>-10,2</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-59,41; 41,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-48,62; 39,77</t>
+          <t>-61,51; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>-59,76; 40,57</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 0,0</t>
+          <t>-45,42; 42,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-65,85; 23,14</t>
+          <t>-65,96; 22,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,0</t>
+          <t>0,0; 51,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 29,61</t>
+          <t>-34,61; 29,38</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-22,79%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-22,64%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>24,49%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-10,43%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-24,98%</t>
+          <t>-5,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-15,37%</t>
+          <t>-11,75%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 68,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,98; 80,9</t>
+          <t>-61,51; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-79,12; 70,52</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 0,0</t>
+          <t>-48,04; 91,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,43; 34,74</t>
+          <t>-77,29; 31,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 170,08</t>
+          <t>0,0; 105,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,51; 42,23</t>
+          <t>-36,73; 43,14</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-4,56</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-5,38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,53</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,23</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-4,56</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 5,07</t>
+          <t>-12,58; 5,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 5,88</t>
+          <t>-14,38; 4,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 10,13</t>
+          <t>-10,36; 8,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 5,63</t>
+          <t>-15,54; 4,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 4,58</t>
+          <t>-14,39; 6,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 8,86</t>
+          <t>-12,75; 8,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 3,19</t>
+          <t>-11,53; 2,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 2,33</t>
+          <t>-10,64; 3,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 6,65</t>
+          <t>-7,75; 6,46</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-3,82%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-5,39%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-6,4%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-4,2%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,43%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,82%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-5,39%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0,05%</t>
+          <t>-1,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-0,19%</t>
+          <t>-0,65%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 6,03</t>
+          <t>-14,2; 7,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 7,26</t>
+          <t>-16,73; 5,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 12,58</t>
+          <t>-11,51; 11,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 6,79</t>
+          <t>-17,75; 5,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 5,79</t>
+          <t>-16,73; 7,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 11,13</t>
+          <t>-14,61; 10,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 4,07</t>
+          <t>-13,05; 3,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 3,01</t>
+          <t>-12,21; 4,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 8,36</t>
+          <t>-8,89; 7,97</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-7,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,34</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,83</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11,58</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-7,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>13,13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>7,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 13,92</t>
+          <t>-15,87; 1,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 13,96</t>
+          <t>-9,36; 6,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 21,17</t>
+          <t>-6,87; 10,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 1,28</t>
+          <t>-5,07; 14,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 7,39</t>
+          <t>-5,46; 13,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 10,66</t>
+          <t>3,44; 22,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 5,04</t>
+          <t>-8,31; 5,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,64</t>
+          <t>-4,88; 8,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 12,36</t>
+          <t>0,64; 13,86</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-9,33%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-1,67%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6,31%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>5,43%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-9,33%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-1,67%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 21,62</t>
+          <t>-18,72; 2,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 21,98</t>
+          <t>-11,09; 9,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 33,27</t>
+          <t>-8,25; 13,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 1,67</t>
+          <t>-6,48; 23,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 10,06</t>
+          <t>-7,21; 21,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 14,68</t>
+          <t>4,5; 35,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 6,92</t>
+          <t>-10,48; 8,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 10,74</t>
+          <t>-6,05; 11,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 17,13</t>
+          <t>0,87; 19,51</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15,75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22,72</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>12,49</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>15,46</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>27,03</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15,75</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,3</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,43</t>
+          <t>26,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24,69</t>
+          <t>24,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 21,59</t>
+          <t>7,32; 23,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 23,93</t>
+          <t>1,28; 18,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,0; 34,53</t>
+          <t>15,0; 30,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,77; 23,98</t>
+          <t>4,39; 22,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 19,89</t>
+          <t>7,08; 24,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,61; 30,26</t>
+          <t>18,71; 34,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 19,35</t>
+          <t>8,53; 19,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,62; 19,07</t>
+          <t>6,14; 18,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,95; 30,97</t>
+          <t>19,05; 30,54</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>26,46%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17,31%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>38,18%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>23,1%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>28,6%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26,46%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>17,31%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,2; 43,57</t>
+          <t>11,29; 43,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,63; 48,01</t>
+          <t>2,01; 33,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,19; 70,15</t>
+          <t>24,2; 55,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,78; 44,04</t>
+          <t>7,44; 45,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 36,36</t>
+          <t>12,2; 48,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,84; 55,5</t>
+          <t>32,19; 71,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,7; 36,56</t>
+          <t>14,26; 37,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,01; 35,11</t>
+          <t>10,24; 34,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,63; 58,1</t>
+          <t>31,56; 56,74</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,59</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4,54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11,17</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>5,96</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>7,4</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>15,5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,54</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,03</t>
+          <t>15,69</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>13,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 11,59</t>
+          <t>-1,05; 9,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 13,02</t>
+          <t>-1,1; 9,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,77; 20,68</t>
+          <t>6,09; 16,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 9,85</t>
+          <t>-0,07; 11,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 9,67</t>
+          <t>2,01; 13,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,61; 16,28</t>
+          <t>10,6; 21,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,44</t>
+          <t>1,33; 9,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,07</t>
+          <t>2,2; 9,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,6; 17,11</t>
+          <t>9,77; 17,07</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>9,0%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>11,19%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>23,43%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,16; 18,8</t>
+          <t>-1,45; 14,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,48; 20,44</t>
+          <t>-1,2; 14,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14,21; 33,0</t>
+          <t>8,16; 24,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 14,57</t>
+          <t>0,0; 17,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 14,27</t>
+          <t>2,95; 21,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,54; 23,78</t>
+          <t>15,44; 33,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,15; 14,41</t>
+          <t>1,91; 13,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,39; 15,07</t>
+          <t>3,11; 14,59</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,78; 25,87</t>
+          <t>13,74; 25,42</t>
         </is>
       </c>
     </row>
